--- a/docs/tampermonkey/发票模板/佰通清关发票模板.xlsx
+++ b/docs/tampermonkey/发票模板/佰通清关发票模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\发货\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\代码\hth123321\docs\tampermonkey\发票模板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA586D8-41E9-41D9-8117-B0B6461E22E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D12ACF-5667-4E22-B560-7C4AE87640B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -347,10 +347,6 @@
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>{{"PlentiVive"}}</t>
-    <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
     <t>{{t.clearance.customs_clearance_material+' / '+t.clearance.customs_clearance_en_material}}</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -395,6 +391,10 @@
   </si>
   <si>
     <t>{{rawShipment.amazonReferenceId}}</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{t.product..brand_name}}</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
 </sst>
@@ -925,6 +925,39 @@
     <xf numFmtId="0" fontId="33" fillId="3" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -940,9 +973,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -952,31 +982,7 @@
     <xf numFmtId="177" fontId="14" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1005,12 +1011,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -1429,58 +1429,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="81.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="42"/>
     </row>
     <row r="2" spans="1:18" s="5" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="31"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="42"/>
     </row>
     <row r="3" spans="1:18" s="5" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="44"/>
+      <c r="B3" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="36"/>
       <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
@@ -1490,101 +1490,101 @@
       <c r="G3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="36"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="31"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="42"/>
     </row>
     <row r="4" spans="1:18" s="5" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
       <c r="G4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="31"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="42"/>
     </row>
     <row r="5" spans="1:18" s="5" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
       <c r="G5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
+      <c r="H5" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
       <c r="L5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="31"/>
+      <c r="M5" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="42"/>
     </row>
     <row r="6" spans="1:18" s="5" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
       <c r="G6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="31"/>
+      <c r="H6" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="42"/>
     </row>
     <row r="7" spans="1:18" s="5" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
       <c r="E7" s="9" t="s">
         <v>12</v>
       </c>
@@ -1592,31 +1592,31 @@
       <c r="G7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
+      <c r="H7" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
       <c r="L7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32"/>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="31"/>
+      <c r="M7" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="42"/>
       <c r="R7" s="11"/>
     </row>
     <row r="8" spans="1:18" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
       <c r="E8" s="9" t="s">
         <v>15</v>
       </c>
@@ -1624,69 +1624,69 @@
       <c r="G8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="29">
         <v>1</v>
       </c>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
       <c r="L8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="31"/>
+      <c r="M8" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="42"/>
     </row>
     <row r="9" spans="1:18" s="5" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
       <c r="G9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32"/>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="31"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="42"/>
       <c r="R9" s="11"/>
     </row>
     <row r="10" spans="1:18" s="5" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="31"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="42"/>
     </row>
     <row r="11" spans="1:18" s="5" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="13" t="s">
@@ -1737,7 +1737,7 @@
       <c r="P11" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="Q11" s="31"/>
+      <c r="Q11" s="42"/>
     </row>
     <row r="12" spans="1:18" s="22" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="20" t="s">
@@ -1757,10 +1757,10 @@
       <c r="M12" s="21"/>
       <c r="N12" s="21"/>
       <c r="O12" s="21"/>
-      <c r="P12" s="54"/>
+      <c r="P12" s="27"/>
     </row>
     <row r="13" spans="1:18" s="25" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="28" t="s">
         <v>43</v>
       </c>
       <c r="B13" s="23" t="s">
@@ -1788,27 +1788,27 @@
         <v>52</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="N13" s="23" t="s">
+      <c r="O13" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="O13" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="P13" s="54" t="s">
-        <v>58</v>
+      <c r="P13" s="27" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:18" s="25" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="28" t="s">
         <v>44</v>
       </c>
       <c r="B14" s="21"/>
@@ -1825,7 +1825,7 @@
       <c r="M14" s="21"/>
       <c r="N14" s="21"/>
       <c r="O14" s="21"/>
-      <c r="P14" s="54"/>
+      <c r="P14" s="27"/>
     </row>
     <row r="15" spans="1:18" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A15" s="15"/>
@@ -1865,13 +1865,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:P2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="H3:P3"/>
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="H10:P10"/>
     <mergeCell ref="Q1:Q11"/>
@@ -1888,6 +1881,13 @@
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:P4"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:P2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="H3:P3"/>
   </mergeCells>
   <phoneticPr fontId="28" type="noConversion"/>
   <conditionalFormatting sqref="B7:D7">
@@ -1954,136 +1954,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="53"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="55"/>
     </row>
     <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="50"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="52"/>
       <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="45"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="50"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="52"/>
     </row>
     <row r="3" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="50"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="52"/>
       <c r="H3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="50"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="52"/>
     </row>
     <row r="4" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
       <c r="H4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="47"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="51"/>
     </row>
     <row r="5" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="50"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="52"/>
     </row>
     <row r="6" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="50"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="9">
